--- a/inasistencias-6A-Electronica/Alumnos-6A-Electronica.xlsx
+++ b/inasistencias-6A-Electronica/Alumnos-6A-Electronica.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="353">
   <si>
     <t xml:space="preserve">totales</t>
   </si>
@@ -367,6 +367,9 @@
     <t xml:space="preserve">2do cua</t>
   </si>
   <si>
+    <t xml:space="preserve">Febrero</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nro</t>
   </si>
   <si>
@@ -487,6 +490,9 @@
     <t xml:space="preserve">esta mal la ganancia y falta link con ism</t>
   </si>
   <si>
+    <t xml:space="preserve">Aprobado</t>
+  </si>
+  <si>
     <t xml:space="preserve">G 5</t>
   </si>
   <si>
@@ -500,6 +506,9 @@
   </si>
   <si>
     <t xml:space="preserve">G 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausente</t>
   </si>
   <si>
     <t xml:space="preserve">no funciona</t>
@@ -1131,7 +1140,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1166,12 +1175,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC107"/>
         <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFDE59"/>
-        <bgColor rgb="FFFFC107"/>
       </patternFill>
     </fill>
     <fill>
@@ -1222,7 +1225,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1255,14 +1258,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1275,15 +1270,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1295,15 +1282,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1319,31 +1306,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1356,7 +1335,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="13">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -1413,7 +1392,6 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -1428,7 +1406,6 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -1444,7 +1421,6 @@
           <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -1512,6 +1488,34 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1550,7 +1554,7 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFDE59"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1738,10 +1742,10 @@
         <v>13</v>
       </c>
       <c r="AV1" s="1"/>
-      <c r="BD1" s="0" t="n">
+      <c r="BD1" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="BE1" s="0" t="n">
+      <c r="BE1" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1888,28 +1892,28 @@
       <c r="AV2" s="7" t="n">
         <v>45994</v>
       </c>
-      <c r="AW2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX2" s="8" t="n">
+      <c r="AW2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX2" s="7" t="n">
         <v>46001</v>
       </c>
-      <c r="AY2" s="8" t="s">
+      <c r="AY2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AZ2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="BB2" s="9" t="s">
+      <c r="AZ2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="BD2" s="9" t="s">
+      <c r="BD2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="BE2" s="9" t="s">
+      <c r="BE2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2018,7 +2022,7 @@
       <c r="AN3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AO3" s="10" t="n">
+      <c r="AO3" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AP3" s="3" t="n">
@@ -2037,7 +2041,7 @@
         <f aca="false">COUNTIF(V3:AK3,"A")</f>
         <v>3</v>
       </c>
-      <c r="AT3" s="11" t="n">
+      <c r="AT3" s="9" t="n">
         <f aca="false">ROUND((AP3+AQ3/2+AR3/4)*10/13,0)</f>
         <v>8</v>
       </c>
@@ -2049,7 +2053,7 @@
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -2163,29 +2167,29 @@
         <f aca="false">COUNTIF(V4:AK4,"A")</f>
         <v>2</v>
       </c>
-      <c r="AT4" s="11" t="n">
+      <c r="AT4" s="9" t="n">
         <f aca="false">ROUND((AP4+AQ4/2+AR4/4)*10/13,0)</f>
         <v>8</v>
       </c>
       <c r="AV4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AX4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AY4" s="9" t="n">
+      <c r="AX4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY4" s="3" t="n">
         <f aca="false">COUNTIF(AV4:AX4,"P")</f>
         <v>2</v>
       </c>
-      <c r="AZ4" s="9" t="n">
+      <c r="AZ4" s="3" t="n">
         <f aca="false">COUNTIF(AV4:AX4,"M")</f>
         <v>0</v>
       </c>
-      <c r="BA4" s="9" t="n">
+      <c r="BA4" s="3" t="n">
         <f aca="false">COUNTIF(AV4:AX4,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB4" s="13" t="n">
+      <c r="BB4" s="9" t="n">
         <f aca="false">ROUND((AY4+AZ4/2+BA4/4)*5,0)</f>
         <v>10</v>
       </c>
@@ -2314,11 +2318,11 @@
         <f aca="false">COUNTIF(V5:AK5,"A")</f>
         <v>1</v>
       </c>
-      <c r="AT5" s="11" t="n">
+      <c r="AT5" s="9" t="n">
         <f aca="false">ROUND((AP5+AQ5/2+AR5/4)*10/13,0)</f>
         <v>9</v>
       </c>
-      <c r="BB5" s="13"/>
+      <c r="BB5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -2407,7 +2411,7 @@
       <c r="AE6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AF6" s="10" t="n">
+      <c r="AF6" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AG6" s="3" t="s">
@@ -2447,11 +2451,11 @@
         <f aca="false">COUNTIF(V6:AK6,"A")</f>
         <v>2</v>
       </c>
-      <c r="AT6" s="11" t="n">
+      <c r="AT6" s="9" t="n">
         <f aca="false">ROUND((AP6+AQ6/2+AR6/4)*10/13,0)</f>
         <v>8</v>
       </c>
-      <c r="BB6" s="13"/>
+      <c r="BB6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -2577,11 +2581,11 @@
         <f aca="false">COUNTIF(V7:AK7,"A")</f>
         <v>1</v>
       </c>
-      <c r="AT7" s="11" t="n">
+      <c r="AT7" s="9" t="n">
         <f aca="false">ROUND((AP7+AQ7/2+AR7/4)*10/13,0)</f>
         <v>9</v>
       </c>
-      <c r="BB7" s="13"/>
+      <c r="BB7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -2590,7 +2594,7 @@
       <c r="B8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -2670,7 +2674,7 @@
       <c r="AE8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AF8" s="10" t="n">
+      <c r="AF8" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AG8" s="3" t="s">
@@ -2710,29 +2714,29 @@
         <f aca="false">COUNTIF(V8:AK8,"A")</f>
         <v>5</v>
       </c>
-      <c r="AT8" s="11" t="n">
+      <c r="AT8" s="9" t="n">
         <f aca="false">ROUND((AP8+AQ8/2+AR8/4)*10/13,0)</f>
         <v>6</v>
       </c>
       <c r="AV8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AX8" s="9" t="s">
+      <c r="AX8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AY8" s="9" t="n">
+      <c r="AY8" s="3" t="n">
         <f aca="false">COUNTIF(AV8:AX8,"P")</f>
         <v>0</v>
       </c>
-      <c r="AZ8" s="9" t="n">
+      <c r="AZ8" s="3" t="n">
         <f aca="false">COUNTIF(AV8:AX8,"M")</f>
         <v>0</v>
       </c>
-      <c r="BA8" s="9" t="n">
+      <c r="BA8" s="3" t="n">
         <f aca="false">COUNTIF(AV8:AX8,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB8" s="13" t="n">
+      <c r="BB8" s="9" t="n">
         <f aca="false">ROUND((AY8+AZ8/2+BA8/4)*5,0)</f>
         <v>0</v>
       </c>
@@ -2858,11 +2862,11 @@
         <f aca="false">COUNTIF(V9:AK9,"A")</f>
         <v>0</v>
       </c>
-      <c r="AT9" s="11" t="n">
+      <c r="AT9" s="9" t="n">
         <f aca="false">ROUND((AP9+AQ9/2+AR9/4)*10/13,0)</f>
         <v>10</v>
       </c>
-      <c r="BB9" s="13"/>
+      <c r="BB9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -2969,7 +2973,7 @@
       <c r="AN10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AO10" s="10" t="n">
+      <c r="AO10" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AP10" s="3" t="n">
@@ -2988,11 +2992,11 @@
         <f aca="false">COUNTIF(V10:AK10,"A")</f>
         <v>1</v>
       </c>
-      <c r="AT10" s="11" t="n">
+      <c r="AT10" s="9" t="n">
         <f aca="false">ROUND((AP10+AQ10/2+AR10/4)*10/13,0)</f>
         <v>9</v>
       </c>
-      <c r="BB10" s="13"/>
+      <c r="BB10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -3115,11 +3119,11 @@
         <f aca="false">COUNTIF(V11:AK11,"A")</f>
         <v>0</v>
       </c>
-      <c r="AT11" s="11" t="n">
+      <c r="AT11" s="9" t="n">
         <f aca="false">ROUND((AP11+AQ11/2+AR11/4)*10/13,0)</f>
         <v>10</v>
       </c>
-      <c r="BB11" s="13"/>
+      <c r="BB11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -3128,7 +3132,7 @@
       <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -3242,12 +3246,12 @@
         <f aca="false">COUNTIF(V12:AK12,"A")</f>
         <v>4</v>
       </c>
-      <c r="AT12" s="11" t="n">
+      <c r="AT12" s="9" t="n">
         <f aca="false">ROUND((AP12+AQ12/2+AR12/4)*10/13,0)</f>
         <v>7</v>
       </c>
       <c r="AV12" s="3"/>
-      <c r="BB12" s="13"/>
+      <c r="BB12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -3370,11 +3374,11 @@
         <f aca="false">COUNTIF(V13:AK13,"A")</f>
         <v>1</v>
       </c>
-      <c r="AT13" s="11" t="n">
+      <c r="AT13" s="9" t="n">
         <f aca="false">ROUND((AP13+AQ13/2+AR13/4)*10/13,0)</f>
         <v>9</v>
       </c>
-      <c r="BB13" s="13"/>
+      <c r="BB13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -3475,7 +3479,7 @@
       <c r="AK14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AL14" s="10" t="n">
+      <c r="AL14" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AM14" s="2" t="s">
@@ -3500,11 +3504,11 @@
         <f aca="false">COUNTIF(V14:AK14,"A")</f>
         <v>5</v>
       </c>
-      <c r="AT14" s="11" t="n">
+      <c r="AT14" s="9" t="n">
         <f aca="false">ROUND((AP14+AQ14/2+AR14/4)*10/13,0)</f>
         <v>6</v>
       </c>
-      <c r="BB14" s="13"/>
+      <c r="BB14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -3566,7 +3570,7 @@
         <f aca="false">ROUND(T15*10/$X$1,0)</f>
         <v>10</v>
       </c>
-      <c r="V15" s="16" t="s">
+      <c r="V15" s="12" t="s">
         <v>19</v>
       </c>
       <c r="X15" s="1" t="s">
@@ -3627,11 +3631,11 @@
         <f aca="false">COUNTIF(V15:AK15,"A")</f>
         <v>0</v>
       </c>
-      <c r="AT15" s="11" t="n">
+      <c r="AT15" s="9" t="n">
         <f aca="false">ROUND((AP15+AQ15/2+AR15/4)*10/13,0)</f>
         <v>10</v>
       </c>
-      <c r="BB15" s="13"/>
+      <c r="BB15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -3754,11 +3758,11 @@
         <f aca="false">COUNTIF(V16:AK16,"A")</f>
         <v>1</v>
       </c>
-      <c r="AT16" s="11" t="n">
+      <c r="AT16" s="9" t="n">
         <f aca="false">ROUND((AP16+AQ16/2+AR16/4)*10/13,0)</f>
         <v>9</v>
       </c>
-      <c r="BB16" s="13"/>
+      <c r="BB16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -3767,7 +3771,7 @@
       <c r="B17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="11" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -3881,32 +3885,32 @@
         <f aca="false">COUNTIF(V17:AK17,"A")</f>
         <v>4</v>
       </c>
-      <c r="AT17" s="11" t="n">
+      <c r="AT17" s="9" t="n">
         <f aca="false">ROUND((AP17+AQ17/2+AR17/4)*10/13,0)</f>
         <v>7</v>
       </c>
       <c r="AV17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AW17" s="10" t="n">
+      <c r="AW17" s="8" t="n">
         <v>0.652777777777778</v>
       </c>
-      <c r="AX17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AY17" s="9" t="n">
+      <c r="AX17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY17" s="3" t="n">
         <f aca="false">COUNTIF(AV17:AX17,"P")</f>
         <v>2</v>
       </c>
-      <c r="AZ17" s="9" t="n">
+      <c r="AZ17" s="3" t="n">
         <f aca="false">COUNTIF(AV17:AX17,"M")</f>
         <v>0</v>
       </c>
-      <c r="BA17" s="9" t="n">
+      <c r="BA17" s="3" t="n">
         <f aca="false">COUNTIF(AV17:AX17,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB17" s="13" t="n">
+      <c r="BB17" s="9" t="n">
         <f aca="false">ROUND((AY17+AZ17/2+BA17/4)*5,0)</f>
         <v>10</v>
       </c>
@@ -3918,7 +3922,7 @@
       <c r="B18" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -4032,29 +4036,29 @@
         <f aca="false">COUNTIF(V18:AK18,"A")</f>
         <v>2</v>
       </c>
-      <c r="AT18" s="11" t="n">
+      <c r="AT18" s="9" t="n">
         <f aca="false">ROUND((AP18+AQ18/2+AR18/4)*10/13,0)</f>
         <v>8</v>
       </c>
       <c r="AV18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AX18" s="9" t="s">
+      <c r="AX18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AY18" s="9" t="n">
+      <c r="AY18" s="3" t="n">
         <f aca="false">COUNTIF(AV18:AX18,"P")</f>
         <v>0</v>
       </c>
-      <c r="AZ18" s="9" t="n">
+      <c r="AZ18" s="3" t="n">
         <f aca="false">COUNTIF(AV18:AX18,"M")</f>
         <v>0</v>
       </c>
-      <c r="BA18" s="9" t="n">
+      <c r="BA18" s="3" t="n">
         <f aca="false">COUNTIF(AV18:AX18,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB18" s="13" t="n">
+      <c r="BB18" s="9" t="n">
         <f aca="false">ROUND((AY18+AZ18/2+BA18/4)*5,0)</f>
         <v>0</v>
       </c>
@@ -4180,11 +4184,11 @@
         <f aca="false">COUNTIF(V19:AK19,"A")</f>
         <v>3</v>
       </c>
-      <c r="AT19" s="11" t="n">
+      <c r="AT19" s="9" t="n">
         <f aca="false">ROUND((AP19+AQ19/2+AR19/4)*10/13,0)</f>
         <v>8</v>
       </c>
-      <c r="BB19" s="13"/>
+      <c r="BB19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -4270,7 +4274,7 @@
       <c r="AE20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AF20" s="10" t="n">
+      <c r="AF20" s="8" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="AG20" s="3" t="s">
@@ -4310,11 +4314,11 @@
         <f aca="false">COUNTIF(V20:AK20,"A")</f>
         <v>0</v>
       </c>
-      <c r="AT20" s="11" t="n">
+      <c r="AT20" s="9" t="n">
         <f aca="false">ROUND((AP20+AQ20/2+AR20/4)*10/13,0)</f>
         <v>10</v>
       </c>
-      <c r="BB20" s="13"/>
+      <c r="BB20" s="9"/>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -4424,7 +4428,7 @@
       <c r="AN21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AO21" s="10" t="n">
+      <c r="AO21" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AP21" s="1" t="n">
@@ -4443,13 +4447,14 @@
         <f aca="false">COUNTIF(V21:AK21,"A")</f>
         <v>0</v>
       </c>
-      <c r="AT21" s="11" t="n">
+      <c r="AT21" s="9" t="n">
         <f aca="false">ROUND((AP21+AQ21/2+AR21/4)*10/13,0)</f>
         <v>10</v>
       </c>
       <c r="AU21" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="BB21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -4458,7 +4463,7 @@
       <c r="B22" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="11" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -4556,7 +4561,7 @@
       <c r="AN22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AO22" s="10" t="n">
+      <c r="AO22" s="8" t="n">
         <v>0.645833333333333</v>
       </c>
       <c r="AP22" s="3" t="n">
@@ -4575,29 +4580,29 @@
         <f aca="false">COUNTIF(V22:AK22,"A")</f>
         <v>5</v>
       </c>
-      <c r="AT22" s="11" t="n">
+      <c r="AT22" s="9" t="n">
         <f aca="false">ROUND((AP22+AQ22/2+AR22/4)*10/13,0)</f>
         <v>6</v>
       </c>
       <c r="AV22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AX22" s="9" t="s">
+      <c r="AX22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AY22" s="9" t="n">
+      <c r="AY22" s="3" t="n">
         <f aca="false">COUNTIF(AV22:AX22,"P")</f>
         <v>0</v>
       </c>
-      <c r="AZ22" s="9" t="n">
+      <c r="AZ22" s="3" t="n">
         <f aca="false">COUNTIF(AV22:AX22,"M")</f>
         <v>0</v>
       </c>
-      <c r="BA22" s="9" t="n">
+      <c r="BA22" s="3" t="n">
         <f aca="false">COUNTIF(AV22:AX22,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB22" s="13" t="n">
+      <c r="BB22" s="9" t="n">
         <f aca="false">ROUND((AY22+AZ22/2+BA22/4)*5,0)</f>
         <v>0</v>
       </c>
@@ -4723,11 +4728,11 @@
         <f aca="false">COUNTIF(V23:AK23,"A")</f>
         <v>2</v>
       </c>
-      <c r="AT23" s="11" t="n">
+      <c r="AT23" s="9" t="n">
         <f aca="false">ROUND((AP23+AQ23/2+AR23/4)*10/13,0)</f>
         <v>8</v>
       </c>
-      <c r="BB23" s="13"/>
+      <c r="BB23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -4850,11 +4855,11 @@
         <f aca="false">COUNTIF(V24:AK24,"A")</f>
         <v>0</v>
       </c>
-      <c r="AT24" s="11" t="n">
+      <c r="AT24" s="9" t="n">
         <f aca="false">ROUND((AP24+AQ24/2+AR24/4)*10/13,0)</f>
         <v>10</v>
       </c>
-      <c r="BB24" s="13"/>
+      <c r="BB24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
@@ -4977,11 +4982,11 @@
         <f aca="false">COUNTIF(V25:AK25,"A")</f>
         <v>2</v>
       </c>
-      <c r="AT25" s="11" t="n">
+      <c r="AT25" s="9" t="n">
         <f aca="false">ROUND((AP25+AQ25/2+AR25/4)*10/13,0)</f>
         <v>8</v>
       </c>
-      <c r="BB25" s="13"/>
+      <c r="BB25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -5055,7 +5060,7 @@
       <c r="Z26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AA26" s="16" t="s">
+      <c r="AA26" s="12" t="s">
         <v>19</v>
       </c>
       <c r="AC26" s="1" t="s">
@@ -5079,7 +5084,7 @@
       <c r="AJ26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AK26" s="16" t="s">
+      <c r="AK26" s="12" t="s">
         <v>19</v>
       </c>
       <c r="AM26" s="2" t="s">
@@ -5104,11 +5109,11 @@
         <f aca="false">COUNTIF(V26:AK26,"A")</f>
         <v>0</v>
       </c>
-      <c r="AT26" s="11" t="n">
+      <c r="AT26" s="9" t="n">
         <f aca="false">ROUND((AP26+AQ26/2+AR26/4)*10/13,0)</f>
         <v>10</v>
       </c>
-      <c r="BB26" s="13"/>
+      <c r="BB26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -5231,11 +5236,11 @@
         <f aca="false">COUNTIF(V27:AK27,"A")</f>
         <v>2</v>
       </c>
-      <c r="AT27" s="11" t="n">
+      <c r="AT27" s="9" t="n">
         <f aca="false">ROUND((AP27+AQ27/2+AR27/4)*10/13,0)</f>
         <v>8</v>
       </c>
-      <c r="BB27" s="13"/>
+      <c r="BB27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -5244,7 +5249,7 @@
       <c r="B28" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="13" t="s">
         <v>102</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -5358,32 +5363,32 @@
         <f aca="false">COUNTIF(V28:AK28,"A")</f>
         <v>2</v>
       </c>
-      <c r="AT28" s="11" t="n">
+      <c r="AT28" s="9" t="n">
         <f aca="false">ROUND((AP28+AQ28/2+AR28/4)*10/13,0)</f>
         <v>8</v>
       </c>
       <c r="AV28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="AW28" s="10" t="n">
+      <c r="AW28" s="8" t="n">
         <v>0.659722222222222</v>
       </c>
-      <c r="AX28" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AY28" s="9" t="n">
+      <c r="AX28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY28" s="3" t="n">
         <f aca="false">COUNTIF(AV28:AX28,"P")</f>
         <v>2</v>
       </c>
-      <c r="AZ28" s="9" t="n">
+      <c r="AZ28" s="3" t="n">
         <f aca="false">COUNTIF(AV28:AX28,"M")</f>
         <v>0</v>
       </c>
-      <c r="BA28" s="9" t="n">
+      <c r="BA28" s="3" t="n">
         <f aca="false">COUNTIF(AV28:AX28,"T")</f>
         <v>0</v>
       </c>
-      <c r="BB28" s="13" t="n">
+      <c r="BB28" s="9" t="n">
         <f aca="false">ROUND((AY28+AZ28/2+BA28/4)*5,0)</f>
         <v>10</v>
       </c>
@@ -5488,11 +5493,11 @@
         <f aca="false">COUNTIF(AN3:AN28,"P")</f>
         <v>17</v>
       </c>
-      <c r="AV29" s="9" t="n">
+      <c r="AV29" s="3" t="n">
         <f aca="false">COUNTIF(AV4:AV28,"P")</f>
         <v>3</v>
       </c>
-      <c r="AX29" s="9" t="n">
+      <c r="AX29" s="3" t="n">
         <f aca="false">COUNTIF(AX4:AX28,"P")</f>
         <v>3</v>
       </c>
@@ -5525,20 +5530,20 @@
         <f aca="false">COUNTIF(AK3:AK28,"M")</f>
         <v>0</v>
       </c>
-      <c r="AM30" s="16" t="n">
+      <c r="AM30" s="12" t="n">
         <f aca="false">COUNTIF(AM3:AM28,"M")</f>
         <v>0</v>
       </c>
-      <c r="AN30" s="16" t="n">
+      <c r="AN30" s="12" t="n">
         <f aca="false">COUNTIF(AN3:AN28,"M")</f>
         <v>0</v>
       </c>
       <c r="AO30" s="3"/>
-      <c r="AV30" s="9" t="n">
+      <c r="AV30" s="3" t="n">
         <f aca="false">COUNTIF(AV4:AV28,"m")</f>
         <v>0</v>
       </c>
-      <c r="AX30" s="9" t="n">
+      <c r="AX30" s="3" t="n">
         <f aca="false">COUNTIF(AX4:AX28,"m")</f>
         <v>0</v>
       </c>
@@ -5571,20 +5576,20 @@
         <f aca="false">COUNTIF(AK3:AK28,"T")</f>
         <v>1</v>
       </c>
-      <c r="AM31" s="16" t="n">
+      <c r="AM31" s="12" t="n">
         <f aca="false">COUNTIF(AM3:AM28,"T")</f>
         <v>0</v>
       </c>
-      <c r="AN31" s="16" t="n">
+      <c r="AN31" s="12" t="n">
         <f aca="false">COUNTIF(AN3:AN28,"T")</f>
         <v>4</v>
       </c>
       <c r="AO31" s="3"/>
-      <c r="AV31" s="9" t="n">
+      <c r="AV31" s="3" t="n">
         <f aca="false">COUNTIF(AV4:AV28,"T")</f>
         <v>0</v>
       </c>
-      <c r="AX31" s="9" t="n">
+      <c r="AX31" s="3" t="n">
         <f aca="false">COUNTIF(AX4:AX28,"T")</f>
         <v>0</v>
       </c>
@@ -5617,20 +5622,20 @@
         <f aca="false">SUM(AK29:AK31)</f>
         <v>24</v>
       </c>
-      <c r="AM32" s="16" t="n">
+      <c r="AM32" s="12" t="n">
         <f aca="false">SUM(AM29:AM31)</f>
         <v>25</v>
       </c>
-      <c r="AN32" s="16" t="n">
+      <c r="AN32" s="12" t="n">
         <f aca="false">SUM(AN29:AN31)</f>
         <v>21</v>
       </c>
       <c r="AO32" s="3"/>
-      <c r="AV32" s="9" t="n">
+      <c r="AV32" s="3" t="n">
         <f aca="false">SUM(AV29:AV31)</f>
         <v>3</v>
       </c>
-      <c r="AX32" s="9" t="n">
+      <c r="AX32" s="3" t="n">
         <f aca="false">SUM(AX29:AX31)</f>
         <v>3</v>
       </c>
@@ -5691,19 +5696,19 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5720,7 +5725,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>0.33</v>
@@ -5785,7 +5790,7 @@
         <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8</v>
@@ -5808,7 +5813,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>6.33</v>
@@ -5859,7 +5864,7 @@
         <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>7.67</v>
@@ -5884,7 +5889,7 @@
         <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7.67</v>
@@ -5904,7 +5909,7 @@
         <v>51</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>0.33</v>
@@ -5941,7 +5946,7 @@
         <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>8.8</v>
@@ -5978,7 +5983,7 @@
         <v>63</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>6.8</v>
@@ -6015,7 +6020,7 @@
         <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7.93</v>
@@ -6040,7 +6045,7 @@
         <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>4.8</v>
@@ -6074,7 +6079,7 @@
         <v>75</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -6097,7 +6102,7 @@
         <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7.67</v>
@@ -6134,7 +6139,7 @@
         <v>86</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
@@ -6157,7 +6162,7 @@
         <v>89</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>8.67</v>
@@ -6180,7 +6185,7 @@
         <v>92</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>8.33</v>
@@ -6203,7 +6208,7 @@
         <v>95</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>9</v>
@@ -6228,7 +6233,7 @@
         <v>95</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>8.67</v>
@@ -6242,7 +6247,7 @@
         <v>95</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>8.13</v>
@@ -6256,7 +6261,7 @@
         <v>95</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>8.13</v>
@@ -6270,7 +6275,7 @@
         <v>95</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>6.33</v>
@@ -6290,7 +6295,7 @@
         <v>98</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>9</v>
@@ -6354,19 +6359,19 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6453,7 +6458,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -6476,7 +6481,7 @@
         <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -6501,7 +6506,7 @@
         <v>42</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>6</v>
@@ -6563,7 +6568,7 @@
         <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -6642,7 +6647,7 @@
         <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -6667,7 +6672,7 @@
         <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>3</v>
@@ -6681,7 +6686,7 @@
         <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -6695,7 +6700,7 @@
         <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -6715,7 +6720,7 @@
         <v>72</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -6752,7 +6757,7 @@
         <v>78</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -6817,7 +6822,7 @@
         <v>92</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>9</v>
@@ -6840,7 +6845,7 @@
         <v>95</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>10</v>
@@ -6917,10 +6922,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6937,7 +6942,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>3.5</v>
@@ -6957,7 +6962,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>3.5</v>
@@ -6977,7 +6982,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8.25</v>
@@ -6997,7 +7002,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2.25</v>
@@ -7017,7 +7022,7 @@
         <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2.75</v>
@@ -7037,7 +7042,7 @@
         <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2</v>
@@ -7057,7 +7062,7 @@
         <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8.5</v>
@@ -7077,7 +7082,7 @@
         <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>6.75</v>
@@ -7097,7 +7102,7 @@
         <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -7117,7 +7122,7 @@
         <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>3.25</v>
@@ -7137,7 +7142,7 @@
         <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7.5</v>
@@ -7157,7 +7162,7 @@
         <v>57</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8.75</v>
@@ -7177,7 +7182,7 @@
         <v>60</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>4.5</v>
@@ -7197,7 +7202,7 @@
         <v>63</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>6</v>
@@ -7217,7 +7222,7 @@
         <v>66</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>3.25</v>
@@ -7237,7 +7242,7 @@
         <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>5.25</v>
@@ -7257,7 +7262,7 @@
         <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -7277,7 +7282,7 @@
         <v>75</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -7297,7 +7302,7 @@
         <v>78</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>5.5</v>
@@ -7317,7 +7322,7 @@
         <v>83</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>2.5</v>
@@ -7337,7 +7342,7 @@
         <v>86</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8.25</v>
@@ -7357,7 +7362,7 @@
         <v>89</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>7.75</v>
@@ -7377,7 +7382,7 @@
         <v>92</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8.75</v>
@@ -7397,7 +7402,7 @@
         <v>95</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>9.5</v>
@@ -7417,7 +7422,7 @@
         <v>98</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -7454,7 +7459,7 @@
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26"/>
+      <c r="A1" s="20"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7472,55 +7477,43 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A5:AU35"/>
+  <dimension ref="A5:AV35"/>
   <sheetFormatPr defaultColWidth="9.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="9.4"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="9.4"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="9.4"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="15.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="6" style="1" width="9.4"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="12.8"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="1" width="9.4"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="12" style="1" width="9.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="9.59"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="23" min="18" style="1" width="9.59"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="23" min="12" style="1" width="9.59"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="24" style="1" width="13.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="18" width="8.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="13.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="18.25"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="28" min="28" style="1" width="9.71"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="25" min="25" style="1" width="8.07"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="1" width="13.93"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="27" min="27" style="1" width="18.25"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="28" style="1" width="9.71"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="30" style="1" width="29.29"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="42" min="31" style="1" width="9.71"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="44" min="43" style="0" width="9.71"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="45" min="31" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="47" min="46" style="0" width="9.71"/>
   </cols>
   <sheetData>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AT5" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU5" s="0" t="n">
-        <v>6</v>
-      </c>
+      <c r="AT5" s="1"/>
+      <c r="AU5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AT6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="AU6" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="AT6" s="3"/>
+      <c r="AU6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AS7" s="9" t="s">
+      <c r="AS7" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="14" t="s">
         <v>108</v>
       </c>
       <c r="V8" s="1" t="s">
@@ -7529,97 +7522,100 @@
       <c r="AI8" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AR8" s="9" t="s">
+      <c r="AR8" s="3" t="s">
         <v>108</v>
+      </c>
+      <c r="AV8" s="15" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="T9" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="U9" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="X9" s="4" t="n">
         <v>45875</v>
       </c>
-      <c r="Y9" s="20" t="s">
-        <v>131</v>
+      <c r="Y9" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AD9" s="1" t="s">
         <v>1</v>
@@ -7628,34 +7624,34 @@
         <v>13</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AL9" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AM9" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AN9" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AO9" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AQ9" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AR9" s="3" t="s">
         <v>13</v>
@@ -7663,8 +7659,11 @@
       <c r="AS9" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AT9" s="9" t="s">
-        <v>144</v>
+      <c r="AT9" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="AV9" s="16" t="n">
+        <v>46080</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7690,24 +7689,24 @@
         <f aca="false">ROUND(I10/2+G10,0)</f>
         <v>9</v>
       </c>
-      <c r="L10" s="11" t="n">
+      <c r="L10" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C10,E10,J10),0)</f>
         <v>9</v>
       </c>
-      <c r="M10" s="1" t="str">
+      <c r="M10" s="9" t="str">
         <f aca="false">IF(L10&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N10" s="21" t="n">
+      <c r="N10" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="O10" s="22" t="n">
+      <c r="O10" s="18" t="n">
         <v>45849</v>
       </c>
-      <c r="P10" s="21" t="n">
+      <c r="P10" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" s="22" t="n">
+      <c r="Q10" s="18" t="n">
         <v>45849</v>
       </c>
       <c r="R10" s="1" t="n">
@@ -7720,7 +7719,7 @@
         <f aca="false">S10+T10/2</f>
         <v>10</v>
       </c>
-      <c r="V10" s="23" t="n">
+      <c r="V10" s="19" t="n">
         <f aca="false">ROUND(AVERAGE(U10,R10,P10,N10,L10),0)</f>
         <v>7</v>
       </c>
@@ -7728,20 +7727,20 @@
         <f aca="false">ROUND(AVERAGE(C10,E10,J10,N10,P10,R10,S10),0)</f>
         <v>8</v>
       </c>
-      <c r="Y10" s="18" t="n">
+      <c r="Y10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC10" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AE10" s="1" t="n">
         <v>8</v>
@@ -7750,139 +7749,142 @@
         <f aca="false">AE10+AF10/2</f>
         <v>8</v>
       </c>
-      <c r="AI10" s="11" t="n">
+      <c r="AI10" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y10,Z10,AC10,AG10),0)</f>
         <v>8</v>
       </c>
-      <c r="AQ10" s="11" t="n">
+      <c r="AQ10" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V10,AI10),0)</f>
         <v>8</v>
       </c>
-      <c r="AR10" s="11"/>
+      <c r="AR10" s="9"/>
       <c r="AS10" s="3" t="n">
         <f aca="false">ROUND(AVERAGE(C11),0)</f>
         <v>9</v>
       </c>
-      <c r="AT10" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="AT10" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="24" t="n">
-        <v>9</v>
-      </c>
-      <c r="D11" s="25" t="n">
+      <c r="C11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="G11" s="24" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" s="25" t="n">
+      <c r="G11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="n">
+      <c r="I11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
         <f aca="false">I11/2+G11</f>
         <v>9</v>
       </c>
-      <c r="L11" s="23" t="n">
+      <c r="L11" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,J11),0)</f>
         <v>7</v>
       </c>
-      <c r="M11" s="23" t="str">
+      <c r="M11" s="9" t="str">
         <f aca="false">IF(L11&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="n">
+      <c r="N11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="2" t="n">
+      <c r="R11" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="S11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="U11" s="2" t="n">
+      <c r="S11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <f aca="false">S11+T11/2</f>
         <v>9</v>
       </c>
-      <c r="V11" s="23" t="n">
+      <c r="V11" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U11,R11,P11,N11,L11),0)</f>
         <v>6</v>
       </c>
-      <c r="W11" s="2" t="n">
+      <c r="W11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,J11,N11,P11,R11,S11),0)</f>
         <v>6</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="X11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y11" s="18" t="n">
+      <c r="Y11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Z11" s="2" t="n">
+      <c r="Z11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AA11" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AB11" s="2" t="s">
+      <c r="AA11" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AC11" s="2" t="n">
+      <c r="AB11" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AD11" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE11" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG11" s="2" t="n">
+      <c r="AD11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG11" s="1" t="n">
         <f aca="false">AE11+AF11/2</f>
         <v>8</v>
       </c>
-      <c r="AI11" s="23" t="n">
+      <c r="AI11" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y11,Z11,AC11,AG11),0)</f>
         <v>7</v>
       </c>
-      <c r="AL11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ11" s="23" t="n">
+      <c r="AL11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ11" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V11,AI11),0)</f>
         <v>7</v>
       </c>
-      <c r="AR11" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS11" s="2" t="n">
+      <c r="AR11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,G11,P11,Y11,Z11,AC11),0)</f>
         <v>7</v>
       </c>
-      <c r="AT11" s="2" t="n">
+      <c r="AT11" s="9" t="n">
         <f aca="false">ROUND(AS11*6/10,0)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AU11" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>3</v>
       </c>
@@ -7905,24 +7907,24 @@
         <f aca="false">I12/2+G12</f>
         <v>17.5</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C12,E12,J12),0)</f>
         <v>10</v>
       </c>
-      <c r="M12" s="1" t="str">
+      <c r="M12" s="9" t="str">
         <f aca="false">IF(L12&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N12" s="21" t="n">
+      <c r="N12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="O12" s="22" t="n">
+      <c r="O12" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="P12" s="21" t="n">
+      <c r="P12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" s="22" t="n">
+      <c r="Q12" s="4" t="n">
         <v>45849</v>
       </c>
       <c r="R12" s="1" t="n">
@@ -7935,7 +7937,7 @@
         <f aca="false">S12+T12/2</f>
         <v>10</v>
       </c>
-      <c r="V12" s="23" t="n">
+      <c r="V12" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U12,R12,P12,N12,L12),0)</f>
         <v>7</v>
       </c>
@@ -7943,14 +7945,14 @@
         <f aca="false">ROUND(AVERAGE(C12,E12,J12,N12,P12,R12,S12),0)</f>
         <v>8</v>
       </c>
-      <c r="Y12" s="18" t="n">
+      <c r="Y12" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z12" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AC12" s="1" t="n">
         <v>6</v>
@@ -7965,20 +7967,21 @@
       <c r="AH12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AI12" s="11" t="n">
+      <c r="AI12" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y12,Z12,AC12,AG12,AH12),0)</f>
         <v>7</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AQ12" s="11" t="n">
+        <v>154</v>
+      </c>
+      <c r="AQ12" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V12,AI12),0)</f>
         <v>7</v>
       </c>
-      <c r="AR12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="29.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR12" s="9"/>
+      <c r="AT12" s="9"/>
+    </row>
+    <row r="13" s="1" customFormat="true" ht="29.85" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>4</v>
       </c>
@@ -8001,24 +8004,24 @@
         <f aca="false">I13/2+G13</f>
         <v>14.5</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="L13" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C13,E13,J13),0)</f>
         <v>11</v>
       </c>
-      <c r="M13" s="1" t="str">
+      <c r="M13" s="9" t="str">
         <f aca="false">IF(L13&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N13" s="21" t="n">
+      <c r="N13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="O13" s="22" t="n">
+      <c r="O13" s="4" t="n">
         <v>45849</v>
       </c>
-      <c r="P13" s="21" t="n">
+      <c r="P13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Q13" s="22" t="n">
+      <c r="Q13" s="4" t="n">
         <v>45849</v>
       </c>
       <c r="R13" s="1" t="n">
@@ -8031,7 +8034,7 @@
         <f aca="false">S13+T13/2</f>
         <v>9</v>
       </c>
-      <c r="V13" s="23" t="n">
+      <c r="V13" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U13,R13,P13,N13,L13),0)</f>
         <v>7</v>
       </c>
@@ -8039,49 +8042,50 @@
         <f aca="false">ROUND(AVERAGE(C13,E13,J13,N13,P13,R13,S13),0)</f>
         <v>8</v>
       </c>
-      <c r="Y13" s="18" t="n">
+      <c r="Y13" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z13" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AC13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AD13" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="AE13" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF13" s="26"/>
+      <c r="AD13" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE13" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF13" s="20"/>
       <c r="AG13" s="1" t="n">
         <f aca="false">AE13+AF13/2</f>
         <v>8</v>
       </c>
-      <c r="AH13" s="26"/>
-      <c r="AI13" s="11" t="n">
+      <c r="AH13" s="20"/>
+      <c r="AI13" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y13,Z13,AC13,AG13),0)</f>
         <v>7</v>
       </c>
-      <c r="AJ13" s="26"/>
+      <c r="AJ13" s="20"/>
       <c r="AL13" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AN13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AQ13" s="11" t="n">
+      <c r="AQ13" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V13,AI13),0)</f>
         <v>7</v>
       </c>
-      <c r="AR13" s="11"/>
+      <c r="AR13" s="9"/>
+      <c r="AT13" s="9"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="14.9" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -8106,11 +8110,11 @@
         <f aca="false">I14/2+G14</f>
         <v>13</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C14,E14,J14),0)</f>
         <v>10</v>
       </c>
-      <c r="M14" s="1" t="str">
+      <c r="M14" s="9" t="str">
         <f aca="false">IF(L14&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -8130,7 +8134,7 @@
         <f aca="false">S14+T14/2</f>
         <v>10</v>
       </c>
-      <c r="V14" s="11" t="n">
+      <c r="V14" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U14,R14,P14,N14,L14),0)</f>
         <v>7</v>
       </c>
@@ -8141,149 +8145,156 @@
       <c r="X14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y14" s="18" t="n">
+      <c r="Y14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="Z14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AC14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AD14" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="AE14" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF14" s="26"/>
+      <c r="AD14" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="AE14" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF14" s="20"/>
       <c r="AG14" s="1" t="n">
         <f aca="false">AE14+AF14/2</f>
         <v>9</v>
       </c>
-      <c r="AH14" s="26"/>
-      <c r="AI14" s="11" t="n">
+      <c r="AH14" s="20"/>
+      <c r="AI14" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y14,Z14,AC14,AG14),0)</f>
         <v>7</v>
       </c>
-      <c r="AJ14" s="26"/>
+      <c r="AJ14" s="20"/>
       <c r="AL14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AQ14" s="11" t="n">
+      <c r="AQ14" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V14,AI14),0)</f>
         <v>7</v>
       </c>
-      <c r="AR14" s="11"/>
-    </row>
-    <row r="15" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="AR14" s="9"/>
+      <c r="AT14" s="9"/>
+    </row>
+    <row r="15" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="n">
+      <c r="C15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="n">
+      <c r="I15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="n">
         <f aca="false">I15/2+G15</f>
         <v>7</v>
       </c>
-      <c r="L15" s="23" t="n">
+      <c r="L15" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,J15),0)</f>
         <v>5</v>
       </c>
-      <c r="M15" s="23" t="str">
+      <c r="M15" s="9" t="str">
         <f aca="false">IF(L15&gt;6,"TEA","TEP")</f>
         <v>TEP</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" s="1" t="n">
         <v>6.33</v>
       </c>
-      <c r="P15" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="R15" s="2" t="n">
+      <c r="P15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="R15" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="S15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="U15" s="2" t="n">
+      <c r="S15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" s="1" t="n">
         <f aca="false">S15+T15/2</f>
         <v>8</v>
       </c>
-      <c r="V15" s="23" t="n">
+      <c r="V15" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U15,R15,P15,N15,L15),0)</f>
         <v>6</v>
       </c>
-      <c r="W15" s="2" t="n">
+      <c r="W15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,J15,N15,P15,R15,S15),0)</f>
         <v>6</v>
       </c>
-      <c r="X15" s="2" t="s">
+      <c r="X15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AC15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE15" s="2" t="n">
+      <c r="Y15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AG15" s="2" t="n">
+      <c r="AG15" s="1" t="n">
         <f aca="false">AE15+AF15/2</f>
         <v>6</v>
       </c>
-      <c r="AI15" s="23" t="n">
+      <c r="AI15" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y15,Z15,AC15,AG15),0)</f>
         <v>2</v>
       </c>
-      <c r="AQ15" s="23" t="n">
+      <c r="AQ15" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V15,AI15),0)</f>
         <v>4</v>
       </c>
-      <c r="AR15" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" s="2" t="n">
+      <c r="AR15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,G15,P15,Y15,Z15,AC15),0)</f>
         <v>4</v>
       </c>
-      <c r="AT15" s="2" t="n">
+      <c r="AT15" s="9" t="n">
         <f aca="false">ROUND(AS15*6/10,0)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AU15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AV15" s="21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -8302,18 +8313,18 @@
         <f aca="false">I16/2+G16</f>
         <v>15</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C16,E16,J16),0)</f>
         <v>12</v>
       </c>
-      <c r="M16" s="1" t="str">
+      <c r="M16" s="9" t="str">
         <f aca="false">IF(L16&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N16" s="21" t="n">
+      <c r="N16" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="O16" s="22" t="n">
+      <c r="O16" s="4" t="n">
         <v>45849</v>
       </c>
       <c r="P16" s="1" t="n">
@@ -8329,7 +8340,7 @@
         <f aca="false">S16+T16/2</f>
         <v>10</v>
       </c>
-      <c r="V16" s="23" t="n">
+      <c r="V16" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U16,R16,P16,N16,L16),0)</f>
         <v>9</v>
       </c>
@@ -8337,23 +8348,23 @@
         <f aca="false">ROUND(AVERAGE(C16,E16,J16,N16,P16,R16,S16),0)</f>
         <v>9</v>
       </c>
-      <c r="Y16" s="18" t="n">
+      <c r="Y16" s="1" t="n">
         <v>6</v>
       </c>
       <c r="Z16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AC16" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AE16" s="1" t="n">
         <v>10</v>
@@ -8362,33 +8373,35 @@
         <f aca="false">AE16+AF16/2</f>
         <v>10</v>
       </c>
-      <c r="AI16" s="11" t="n">
+      <c r="AI16" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y16,Z16,AC16,AG16),0)</f>
         <v>8</v>
       </c>
-      <c r="AQ16" s="11" t="n">
+      <c r="AQ16" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V16,AI16),0)</f>
         <v>9</v>
       </c>
-      <c r="AR16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR16" s="9"/>
+      <c r="AT16" s="9"/>
+      <c r="AV16" s="21"/>
+    </row>
+    <row r="17" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>45784</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="1" t="n">
         <v>8</v>
       </c>
       <c r="H17" s="4" t="n">
@@ -8401,24 +8414,24 @@
         <f aca="false">I17/2+G17</f>
         <v>14</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,J17),0)</f>
         <v>10</v>
       </c>
-      <c r="M17" s="1" t="str">
+      <c r="M17" s="9" t="str">
         <f aca="false">IF(L17&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N17" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="O17" s="22" t="n">
+      <c r="N17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>45850</v>
       </c>
-      <c r="P17" s="21" t="n">
+      <c r="P17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Q17" s="22" t="n">
+      <c r="Q17" s="4" t="n">
         <v>45850</v>
       </c>
       <c r="R17" s="1" t="n">
@@ -8431,7 +8444,7 @@
         <f aca="false">S17+T17/2</f>
         <v>10</v>
       </c>
-      <c r="V17" s="23" t="n">
+      <c r="V17" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U17,R17,P17,N17,L17),0)</f>
         <v>9</v>
       </c>
@@ -8439,49 +8452,51 @@
         <f aca="false">ROUND(AVERAGE(C17,E17,J17,N17,P17,R17,S17),0)</f>
         <v>9</v>
       </c>
-      <c r="Y17" s="18" t="n">
+      <c r="Y17" s="1" t="n">
         <v>8</v>
       </c>
       <c r="Z17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AD17" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE17" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF17" s="26"/>
+      <c r="AD17" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE17" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF17" s="20"/>
       <c r="AG17" s="1" t="n">
         <f aca="false">AE17+AF17/2</f>
         <v>9</v>
       </c>
-      <c r="AH17" s="26"/>
-      <c r="AI17" s="11" t="n">
+      <c r="AH17" s="20"/>
+      <c r="AI17" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y17,Z17,AC17,AG17),0)</f>
         <v>8</v>
       </c>
-      <c r="AJ17" s="26"/>
-      <c r="AQ17" s="11" t="n">
+      <c r="AJ17" s="20"/>
+      <c r="AQ17" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V17,AI17),0)</f>
         <v>9</v>
       </c>
-      <c r="AR17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR17" s="9"/>
+      <c r="AT17" s="9"/>
+      <c r="AV17" s="21"/>
+    </row>
+    <row r="18" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -8500,11 +8515,11 @@
         <f aca="false">I18/2+G18</f>
         <v>26.5</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C18,E18,J18),0)</f>
         <v>15</v>
       </c>
-      <c r="M18" s="1" t="str">
+      <c r="M18" s="9" t="str">
         <f aca="false">IF(L18&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -8512,10 +8527,10 @@
         <f aca="false">ROUND(MAX(M18,L18),0)</f>
         <v>15</v>
       </c>
-      <c r="P18" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q18" s="22" t="n">
+      <c r="P18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>45850</v>
       </c>
       <c r="R18" s="1" t="n">
@@ -8528,7 +8543,7 @@
         <f aca="false">S18+T18/2</f>
         <v>10</v>
       </c>
-      <c r="V18" s="23" t="n">
+      <c r="V18" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U18,R18,P18,N18,L18),0)</f>
         <v>12</v>
       </c>
@@ -8536,14 +8551,14 @@
         <f aca="false">ROUND(AVERAGE(C18,E18,J18,N18,P18,R18,S18),0)</f>
         <v>13</v>
       </c>
-      <c r="Y18" s="18" t="n">
+      <c r="Y18" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Z18" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AC18" s="1" t="n">
         <v>10</v>
@@ -8555,24 +8570,26 @@
         <f aca="false">AE18+AF18/2</f>
         <v>10</v>
       </c>
-      <c r="AI18" s="11" t="n">
+      <c r="AI18" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y18,Z18,AC18,AG18),0)</f>
         <v>10</v>
       </c>
       <c r="AL18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AQ18" s="11" t="n">
+      <c r="AQ18" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V18,AI18),0)</f>
         <v>11</v>
       </c>
-      <c r="AR18" s="11"/>
+      <c r="AR18" s="9"/>
+      <c r="AT18" s="9"/>
+      <c r="AV18" s="21"/>
     </row>
     <row r="19" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C19" s="1" t="n">
@@ -8591,11 +8608,11 @@
         <f aca="false">I19/2+G19</f>
         <v>13</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C19,E19,J19),0)</f>
         <v>8</v>
       </c>
-      <c r="M19" s="1" t="str">
+      <c r="M19" s="9" t="str">
         <f aca="false">IF(L19&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -8624,7 +8641,7 @@
         <f aca="false">S19+T19/2</f>
         <v>15</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U19,R19,P19,N19,L19),0)</f>
         <v>7</v>
       </c>
@@ -8635,14 +8652,14 @@
       <c r="X19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y19" s="18" t="n">
+      <c r="Y19" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AC19" s="1" t="n">
         <v>1</v>
@@ -8660,21 +8677,23 @@
       <c r="AH19" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AI19" s="11" t="n">
+      <c r="AI19" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y19,Z19,AC19,AG19,AH19),0)</f>
         <v>7</v>
       </c>
-      <c r="AQ19" s="11" t="n">
+      <c r="AQ19" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V19,AI19),0)</f>
         <v>7</v>
       </c>
-      <c r="AR19" s="11"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR19" s="9"/>
+      <c r="AT19" s="9"/>
+      <c r="AV19" s="21"/>
+    </row>
+    <row r="20" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C20" s="1" t="n">
@@ -8693,11 +8712,11 @@
         <f aca="false">I20/2+G20</f>
         <v>20</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C20,E20,J20),0)</f>
         <v>13</v>
       </c>
-      <c r="M20" s="1" t="str">
+      <c r="M20" s="9" t="str">
         <f aca="false">IF(L20&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -8717,7 +8736,7 @@
         <f aca="false">S20+T20/2</f>
         <v>10</v>
       </c>
-      <c r="V20" s="23" t="n">
+      <c r="V20" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U20,R20,P20,N20,L20),0)</f>
         <v>8</v>
       </c>
@@ -8725,23 +8744,23 @@
         <f aca="false">ROUND(AVERAGE(C20,E20,J20,N20,P20,R20,S20),0)</f>
         <v>10</v>
       </c>
-      <c r="Y20" s="18" t="n">
+      <c r="Y20" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z20" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AA20" s="27" t="s">
-        <v>162</v>
+      <c r="AA20" s="22" t="s">
+        <v>165</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AC20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AE20" s="1" t="n">
         <v>9</v>
@@ -8750,30 +8769,32 @@
         <f aca="false">AE20+AF20/2</f>
         <v>9</v>
       </c>
-      <c r="AI20" s="11" t="n">
+      <c r="AI20" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y20,Z20,AC20,AG20),0)</f>
         <v>7</v>
       </c>
-      <c r="AQ20" s="11" t="n">
+      <c r="AQ20" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V20,AI20),0)</f>
         <v>8</v>
       </c>
-      <c r="AR20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="21.2" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="AR20" s="9"/>
+      <c r="AT20" s="9"/>
+      <c r="AV20" s="21"/>
+    </row>
+    <row r="21" s="1" customFormat="true" ht="21.2" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>45782</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F21" s="4" t="n">
@@ -8789,21 +8810,21 @@
         <f aca="false">I21/2+G21</f>
         <v>8</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C21,E21,J21),0)</f>
         <v>8</v>
       </c>
-      <c r="M21" s="1" t="str">
+      <c r="M21" s="9" t="str">
         <f aca="false">IF(L21&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
       <c r="N21" s="1" t="n">
         <v>8.8</v>
       </c>
-      <c r="P21" s="21" t="n">
+      <c r="P21" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" s="22" t="n">
+      <c r="Q21" s="4" t="n">
         <v>45849</v>
       </c>
       <c r="R21" s="1" t="n">
@@ -8816,7 +8837,7 @@
         <f aca="false">S21+T21/2</f>
         <v>8</v>
       </c>
-      <c r="V21" s="23" t="n">
+      <c r="V21" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U21,R21,P21,N21,L21),0)</f>
         <v>8</v>
       </c>
@@ -8824,23 +8845,23 @@
         <f aca="false">ROUND(AVERAGE(C21,E21,J21,N21,P21,R21,S21),0)</f>
         <v>8</v>
       </c>
-      <c r="Y21" s="18" t="n">
+      <c r="Y21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="Z21" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AA21" s="26" t="s">
-        <v>164</v>
+      <c r="AA21" s="20" t="s">
+        <v>167</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AC21" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AE21" s="1" t="n">
         <v>6</v>
@@ -8852,24 +8873,26 @@
         <f aca="false">AE21+AF21/2</f>
         <v>16</v>
       </c>
-      <c r="AI21" s="11" t="n">
+      <c r="AI21" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y21,Z21,AC21,AG21),0)</f>
         <v>9</v>
       </c>
       <c r="AL21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AQ21" s="11" t="n">
+      <c r="AQ21" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V21,AI21),0)</f>
         <v>9</v>
       </c>
-      <c r="AR21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR21" s="9"/>
+      <c r="AT21" s="9"/>
+      <c r="AV21" s="21"/>
+    </row>
+    <row r="22" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="1" t="n">
@@ -8888,24 +8911,24 @@
         <f aca="false">I22/2+G22</f>
         <v>50.5</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C22,E22,J22),0)</f>
         <v>23</v>
       </c>
-      <c r="M22" s="1" t="str">
+      <c r="M22" s="9" t="str">
         <f aca="false">IF(L22&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N22" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="O22" s="22" t="n">
+      <c r="N22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O22" s="4" t="n">
         <v>45850</v>
       </c>
-      <c r="P22" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q22" s="22" t="n">
+      <c r="P22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>45850</v>
       </c>
       <c r="R22" s="1" t="n">
@@ -8918,7 +8941,7 @@
         <f aca="false">S22+T22/2</f>
         <v>10</v>
       </c>
-      <c r="V22" s="23" t="n">
+      <c r="V22" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U22,R22,P22,N22,L22),0)</f>
         <v>11</v>
       </c>
@@ -8926,17 +8949,17 @@
         <f aca="false">ROUND(AVERAGE(C22,E22,J22,N22,P22,R22,S22),0)</f>
         <v>15</v>
       </c>
-      <c r="Y22" s="18" t="n">
+      <c r="Y22" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Z22" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AC22" s="1" t="n">
         <v>9</v>
@@ -8948,21 +8971,23 @@
         <f aca="false">AE22+AF22/2</f>
         <v>9</v>
       </c>
-      <c r="AI22" s="11" t="n">
+      <c r="AI22" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y22,Z22,AC22,AG22),0)</f>
         <v>9</v>
       </c>
-      <c r="AQ22" s="11" t="n">
+      <c r="AQ22" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V22,AI22),0)</f>
         <v>10</v>
       </c>
-      <c r="AR22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR22" s="9"/>
+      <c r="AT22" s="9"/>
+      <c r="AV22" s="21"/>
+    </row>
+    <row r="23" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="1" t="n">
@@ -8984,11 +9009,11 @@
       <c r="K23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C23,E23,J23,K23),0)</f>
         <v>16</v>
       </c>
-      <c r="M23" s="1" t="str">
+      <c r="M23" s="9" t="str">
         <f aca="false">IF(L23&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -9008,7 +9033,7 @@
         <f aca="false">S23+T23/2</f>
         <v>10</v>
       </c>
-      <c r="V23" s="23" t="n">
+      <c r="V23" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U23,R23,P23,N23,L23),0)</f>
         <v>8</v>
       </c>
@@ -9016,17 +9041,17 @@
         <f aca="false">ROUND(AVERAGE(C23,E23,J23,N23,P23,R23,S23),0)</f>
         <v>11</v>
       </c>
-      <c r="Y23" s="18" t="n">
+      <c r="Y23" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Z23" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AC23" s="1" t="n">
         <v>9</v>
@@ -9038,227 +9063,239 @@
         <f aca="false">AE23+AF23/2</f>
         <v>9</v>
       </c>
-      <c r="AI23" s="11" t="n">
+      <c r="AI23" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y23,Z23,AC23,AG23),0)</f>
         <v>9</v>
       </c>
       <c r="AL23" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AQ23" s="11" t="n">
+      <c r="AQ23" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V23,AI23),0)</f>
         <v>9</v>
       </c>
-      <c r="AR23" s="11"/>
-    </row>
-    <row r="24" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+      <c r="AR23" s="9"/>
+      <c r="AT23" s="9"/>
+      <c r="AV23" s="21"/>
+    </row>
+    <row r="24" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H24" s="28" t="n">
+      <c r="B24" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" s="7" t="n">
         <v>45784</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I24" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="1" t="n">
         <f aca="false">I24/2+G24</f>
         <v>10.5</v>
       </c>
-      <c r="L24" s="23" t="n">
+      <c r="L24" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C24,E24,J24),0)</f>
         <v>9</v>
       </c>
-      <c r="M24" s="23" t="str">
+      <c r="M24" s="9" t="str">
         <f aca="false">IF(L24&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q24" s="28" t="n">
+      <c r="N24" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q24" s="7" t="n">
         <v>45849</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="R24" s="1" t="n">
         <v>3.25</v>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="S24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="U24" s="2" t="n">
+      <c r="U24" s="1" t="n">
         <f aca="false">S24+T24/2</f>
         <v>7</v>
       </c>
-      <c r="V24" s="23" t="n">
+      <c r="V24" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U24,R24,P24,N24,L24),0)</f>
         <v>6</v>
       </c>
-      <c r="W24" s="2" t="n">
+      <c r="W24" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C24,E24,J24,N24,P24,R24,S24),0)</f>
         <v>7</v>
       </c>
-      <c r="X24" s="2" t="s">
+      <c r="X24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y24" s="18" t="n">
+      <c r="Y24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Z24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE24" s="2" t="n">
+      <c r="Z24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="AC24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG24" s="2" t="n">
+      <c r="AG24" s="1" t="n">
         <f aca="false">AE24+AF24/2</f>
         <v>7</v>
       </c>
-      <c r="AI24" s="23" t="n">
+      <c r="AI24" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y24,Z24,AC24,AG24),0)</f>
         <v>4</v>
       </c>
-      <c r="AQ24" s="23" t="n">
+      <c r="AQ24" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V24,AI24),0)</f>
         <v>5</v>
       </c>
-      <c r="AR24" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS24" s="2" t="n">
+      <c r="AR24" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS24" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C24,E24,G24,P24,Y24,Z24,AC24),0)</f>
         <v>5</v>
       </c>
-      <c r="AT24" s="2" t="n">
+      <c r="AT24" s="9" t="n">
         <f aca="false">ROUND(AS24*6/10,0)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="25" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
+      <c r="AU24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AV24" s="21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" s="28" t="n">
+      <c r="C25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="7" t="n">
         <v>45784</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G25" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="1" t="n">
         <f aca="false">I25/2+G25</f>
         <v>8</v>
       </c>
-      <c r="L25" s="23" t="n">
+      <c r="L25" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C25,E25,J25),0)</f>
         <v>9</v>
       </c>
-      <c r="M25" s="23" t="str">
+      <c r="M25" s="9" t="str">
         <f aca="false">IF(L25&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="N25" s="1" t="n">
         <f aca="false">ROUND(MAX(M26,L26),0)</f>
         <v>9</v>
       </c>
-      <c r="P25" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="R25" s="2" t="n">
+      <c r="P25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="R25" s="1" t="n">
         <v>5.25</v>
       </c>
-      <c r="S25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="U25" s="2" t="n">
+      <c r="S25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="U25" s="1" t="n">
         <f aca="false">S25+T25/2</f>
         <v>10</v>
       </c>
-      <c r="V25" s="23" t="n">
+      <c r="V25" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U25,R25,P25,N25,L25),0)</f>
         <v>8</v>
       </c>
-      <c r="W25" s="2" t="n">
+      <c r="W25" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C25,E25,J25,N25,P25,R25,S25),0)</f>
         <v>8</v>
       </c>
-      <c r="Y25" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="2" t="n">
+      <c r="Y25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AA25" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AB25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AC25" s="2" t="n">
+      <c r="AA25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC25" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AD25" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AE25" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG25" s="2" t="n">
+      <c r="AD25" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG25" s="1" t="n">
         <f aca="false">AE25+AF25/2</f>
         <v>8</v>
       </c>
-      <c r="AI25" s="23" t="n">
+      <c r="AI25" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y25,Z25,AC25,AG25),0)</f>
         <v>4</v>
       </c>
-      <c r="AQ25" s="23" t="n">
+      <c r="AQ25" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V25,AI25),0)</f>
         <v>6</v>
       </c>
-      <c r="AR25" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" s="2" t="n">
+      <c r="AR25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C25,E25,G25,P25,Y25,Z25,AC25),0)</f>
         <v>6</v>
       </c>
-      <c r="AT25" s="2" t="n">
+      <c r="AT25" s="9" t="n">
         <f aca="false">ROUND(AS25*6/10,0)</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AU25" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AV25" s="21"/>
+    </row>
+    <row r="26" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>16</v>
       </c>
@@ -9281,11 +9318,11 @@
         <f aca="false">I26/2+G26</f>
         <v>9.5</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C26,E26,J26),0)</f>
         <v>9</v>
       </c>
-      <c r="M26" s="1" t="str">
+      <c r="M26" s="9" t="str">
         <f aca="false">IF(L26&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -9305,7 +9342,7 @@
         <f aca="false">S26+T26/2</f>
         <v>9</v>
       </c>
-      <c r="V26" s="23" t="n">
+      <c r="V26" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U26,R26,P26,N26,L26),0)</f>
         <v>7</v>
       </c>
@@ -9313,23 +9350,23 @@
         <f aca="false">ROUND(AVERAGE(C26,E26,J26,N26,P26,R26,S26),0)</f>
         <v>8</v>
       </c>
-      <c r="Y26" s="18" t="n">
+      <c r="Y26" s="1" t="n">
         <v>3</v>
       </c>
       <c r="Z26" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AC26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AE26" s="1" t="n">
         <v>8</v>
@@ -9341,17 +9378,19 @@
       <c r="AH26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AI26" s="11" t="n">
+      <c r="AI26" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y26,Z26,AC26,AG26,AH26),0)</f>
         <v>7</v>
       </c>
-      <c r="AQ26" s="11" t="n">
+      <c r="AQ26" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V26,AI26),0)</f>
         <v>7</v>
       </c>
-      <c r="AR26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR26" s="9"/>
+      <c r="AT26" s="9"/>
+      <c r="AV26" s="21"/>
+    </row>
+    <row r="27" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>17</v>
       </c>
@@ -9364,11 +9403,11 @@
       <c r="E27" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G27" s="29" t="n">
+      <c r="G27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I27" s="1" t="n">
         <v>25</v>
@@ -9380,11 +9419,11 @@
       <c r="K27" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C27,E27,J27,K27),0)</f>
         <v>12</v>
       </c>
-      <c r="M27" s="1" t="str">
+      <c r="M27" s="9" t="str">
         <f aca="false">IF(L27&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -9404,7 +9443,7 @@
         <f aca="false">S27+T27/2</f>
         <v>6</v>
       </c>
-      <c r="V27" s="23" t="n">
+      <c r="V27" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U27,R27,P27,N27,L27),0)</f>
         <v>7</v>
       </c>
@@ -9415,17 +9454,17 @@
       <c r="X27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y27" s="18" t="n">
+      <c r="Y27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z27" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AC27" s="1" t="n">
         <v>7</v>
@@ -9437,18 +9476,20 @@
         <f aca="false">AE27+AF27/2</f>
         <v>10</v>
       </c>
-      <c r="AI27" s="11" t="n">
+      <c r="AI27" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y27,Z27,AC27,AG27),0)</f>
         <v>7</v>
       </c>
       <c r="AL27" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AQ27" s="11" t="n">
+      <c r="AQ27" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V27,AI27),0)</f>
         <v>7</v>
       </c>
-      <c r="AR27" s="11"/>
+      <c r="AR27" s="9"/>
+      <c r="AT27" s="9"/>
+      <c r="AV27" s="21"/>
     </row>
     <row r="28" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -9473,11 +9514,11 @@
         <f aca="false">I28/2+G28</f>
         <v>11</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C28,E28,J28),0)</f>
         <v>10</v>
       </c>
-      <c r="M28" s="1" t="str">
+      <c r="M28" s="9" t="str">
         <f aca="false">IF(L28&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -9497,7 +9538,7 @@
         <f aca="false">S28+T28/2</f>
         <v>10</v>
       </c>
-      <c r="V28" s="23" t="n">
+      <c r="V28" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U28,R28,P28,N28,L28),0)</f>
         <v>9</v>
       </c>
@@ -9505,151 +9546,159 @@
         <f aca="false">ROUND(AVERAGE(C28,E28,J28,N28,P28,R28,S28),0)</f>
         <v>9</v>
       </c>
-      <c r="Y28" s="18" t="n">
+      <c r="Y28" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z28" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC28" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AD28" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="AE28" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF28" s="27"/>
+      <c r="AD28" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE28" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF28" s="22"/>
       <c r="AG28" s="1" t="n">
         <f aca="false">AE28+AF28/2</f>
         <v>10</v>
       </c>
-      <c r="AH28" s="27"/>
-      <c r="AI28" s="11" t="n">
+      <c r="AH28" s="22"/>
+      <c r="AI28" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y28,Z28,AC28,AG28),0)</f>
         <v>8</v>
       </c>
-      <c r="AJ28" s="27"/>
-      <c r="AQ28" s="11" t="n">
+      <c r="AJ28" s="22"/>
+      <c r="AQ28" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V28,AI28),0)</f>
         <v>9</v>
       </c>
-      <c r="AR28" s="11"/>
-    </row>
-    <row r="29" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B29" s="14" t="s">
+      <c r="AR28" s="9"/>
+      <c r="AT28" s="9"/>
+      <c r="AV28" s="21"/>
+    </row>
+    <row r="29" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="2" t="n">
+      <c r="C29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" s="1" t="n">
         <f aca="false">I29/2+G29</f>
         <v>5</v>
       </c>
-      <c r="L29" s="23" t="n">
+      <c r="L29" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C29,E29,J29),0)</f>
         <v>2</v>
       </c>
-      <c r="M29" s="23" t="str">
+      <c r="M29" s="9" t="str">
         <f aca="false">IF(L29&gt;6,"TEA","TEP")</f>
         <v>TEP</v>
       </c>
-      <c r="N29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" s="2" t="n">
+      <c r="N29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="S29" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="U29" s="2" t="n">
+      <c r="S29" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" s="1" t="n">
         <f aca="false">S29+T29/2</f>
         <v>9</v>
       </c>
-      <c r="V29" s="23" t="n">
+      <c r="V29" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U29,R29,P29,N29,L29),0)</f>
         <v>3</v>
       </c>
-      <c r="W29" s="2" t="n">
+      <c r="W29" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C29,E29,J29,N29,P29,R29,S29),0)</f>
         <v>3</v>
       </c>
-      <c r="X29" s="2" t="s">
+      <c r="X29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y29" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="2" t="n">
+      <c r="Y29" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="AA29" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AB29" s="2" t="s">
+      <c r="AA29" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AC29" s="2" t="n">
+      <c r="AB29" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC29" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="AD29" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="AE29" s="2" t="n">
+      <c r="AD29" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE29" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="AG29" s="2" t="n">
+      <c r="AG29" s="1" t="n">
         <f aca="false">AE29+AF29/2</f>
         <v>6</v>
       </c>
-      <c r="AI29" s="23" t="n">
+      <c r="AI29" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y29,Z29,AC29,AG29),0)</f>
         <v>6</v>
       </c>
-      <c r="AL29" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ29" s="23" t="n">
+      <c r="AL29" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ29" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V29,AI29),0)</f>
         <v>5</v>
       </c>
-      <c r="AR29" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" s="2" t="n">
+      <c r="AR29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C29,E29,G29,P29,Y29,Z29,AC29),0)</f>
         <v>3</v>
       </c>
-      <c r="AT29" s="2" t="n">
+      <c r="AT29" s="9" t="n">
         <f aca="false">ROUND(AS29*6/10,0)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AU29" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AV29" s="21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>20</v>
       </c>
@@ -9672,21 +9721,21 @@
         <f aca="false">I30/2+G30</f>
         <v>12</v>
       </c>
-      <c r="L30" s="11" t="n">
+      <c r="L30" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C30,E30,J30),0)</f>
         <v>10</v>
       </c>
-      <c r="M30" s="1" t="str">
+      <c r="M30" s="9" t="str">
         <f aca="false">IF(L30&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="P30" s="21" t="n">
+      <c r="P30" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="Q30" s="22" t="n">
+      <c r="Q30" s="4" t="n">
         <v>45849</v>
       </c>
       <c r="R30" s="1" t="n">
@@ -9699,7 +9748,7 @@
         <f aca="false">S30+T30/2</f>
         <v>9</v>
       </c>
-      <c r="V30" s="23" t="n">
+      <c r="V30" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U30,R30,P30,N30,L30),0)</f>
         <v>8</v>
       </c>
@@ -9707,23 +9756,23 @@
         <f aca="false">ROUND(AVERAGE(C30,E30,J30,N30,P30,R30,S30),0)</f>
         <v>9</v>
       </c>
-      <c r="Y30" s="18" t="n">
+      <c r="Y30" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Z30" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC30" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AE30" s="1" t="n">
         <v>8</v>
@@ -9732,17 +9781,18 @@
         <f aca="false">AE30+AF30/2</f>
         <v>8</v>
       </c>
-      <c r="AI30" s="11" t="n">
+      <c r="AI30" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y30,Z30,AC30,AG30),0)</f>
         <v>8</v>
       </c>
-      <c r="AQ30" s="11" t="n">
+      <c r="AQ30" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V30,AI30),0)</f>
         <v>8</v>
       </c>
-      <c r="AR30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR30" s="9"/>
+      <c r="AT30" s="9"/>
+    </row>
+    <row r="31" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>21</v>
       </c>
@@ -9765,11 +9815,11 @@
         <f aca="false">I31/2+G31</f>
         <v>19</v>
       </c>
-      <c r="L31" s="11" t="n">
+      <c r="L31" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C31,E31,J31),0)</f>
         <v>13</v>
       </c>
-      <c r="M31" s="1" t="str">
+      <c r="M31" s="9" t="str">
         <f aca="false">IF(L31&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -9789,7 +9839,7 @@
         <f aca="false">S31+T31/2</f>
         <v>10</v>
       </c>
-      <c r="V31" s="23" t="n">
+      <c r="V31" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U31,R31,P31,N31,L31),0)</f>
         <v>8</v>
       </c>
@@ -9797,20 +9847,20 @@
         <f aca="false">ROUND(AVERAGE(C31,E31,J31,N31,P31,R31,S31),0)</f>
         <v>9</v>
       </c>
-      <c r="Y31" s="18" t="n">
+      <c r="Y31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Z31" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AC31" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AE31" s="1" t="n">
         <v>10</v>
@@ -9819,20 +9869,21 @@
         <f aca="false">AE31+AF31/2</f>
         <v>10</v>
       </c>
-      <c r="AI31" s="11" t="n">
+      <c r="AI31" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y31,Z31,AC31,AG31),0)</f>
         <v>9</v>
       </c>
       <c r="AL31" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AQ31" s="11" t="n">
+      <c r="AQ31" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V31,AI31),0)</f>
         <v>9</v>
       </c>
-      <c r="AR31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR31" s="9"/>
+      <c r="AT31" s="9"/>
+    </row>
+    <row r="32" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>22</v>
       </c>
@@ -9855,11 +9906,11 @@
         <f aca="false">I32/2+G32</f>
         <v>58.5</v>
       </c>
-      <c r="L32" s="11" t="n">
+      <c r="L32" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C32,E32,J32),0)</f>
         <v>26</v>
       </c>
-      <c r="M32" s="1" t="str">
+      <c r="M32" s="9" t="str">
         <f aca="false">IF(L32&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -9879,7 +9930,7 @@
         <f aca="false">S32+T32/2</f>
         <v>10</v>
       </c>
-      <c r="V32" s="23" t="n">
+      <c r="V32" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U32,R32,P32,N32,L32),0)</f>
         <v>12</v>
       </c>
@@ -9887,14 +9938,14 @@
         <f aca="false">ROUND(AVERAGE(C32,E32,J32,N32,P32,R32,S32),0)</f>
         <v>16</v>
       </c>
-      <c r="Y32" s="18" t="n">
+      <c r="Y32" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Z32" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AC32" s="1" t="n">
         <v>10</v>
@@ -9906,17 +9957,18 @@
         <f aca="false">AE32+AF32/2</f>
         <v>8</v>
       </c>
-      <c r="AI32" s="11" t="n">
+      <c r="AI32" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y32,Z32,AC32,AG32),0)</f>
         <v>10</v>
       </c>
-      <c r="AQ32" s="11" t="n">
+      <c r="AQ32" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V32,AI32),0)</f>
         <v>11</v>
       </c>
-      <c r="AR32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR32" s="9"/>
+      <c r="AT32" s="9"/>
+    </row>
+    <row r="33" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>23</v>
       </c>
@@ -9942,11 +9994,11 @@
       <c r="K33" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C33,E33,J33,K33),0)</f>
         <v>22</v>
       </c>
-      <c r="M33" s="1" t="str">
+      <c r="M33" s="9" t="str">
         <f aca="false">IF(L33&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
@@ -9967,7 +10019,7 @@
         <f aca="false">S33+T33/2</f>
         <v>10</v>
       </c>
-      <c r="V33" s="23" t="n">
+      <c r="V33" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U33,R33,P33,N33,L33),0)</f>
         <v>12</v>
       </c>
@@ -9975,14 +10027,14 @@
         <f aca="false">ROUND(AVERAGE(C33,E33,J33,N33,P33,R33,S33),0)</f>
         <v>17</v>
       </c>
-      <c r="Y33" s="18" t="n">
+      <c r="Y33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Z33" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AC33" s="1" t="n">
         <v>10</v>
@@ -9994,17 +10046,18 @@
         <f aca="false">AE33+AF33/2</f>
         <v>8</v>
       </c>
-      <c r="AI33" s="11" t="n">
+      <c r="AI33" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y33,Z33,AC33,AG33),0)</f>
         <v>10</v>
       </c>
-      <c r="AQ33" s="11" t="n">
+      <c r="AQ33" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V33,AI33),0)</f>
         <v>11</v>
       </c>
-      <c r="AR33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AR33" s="9"/>
+      <c r="AT33" s="9"/>
+    </row>
+    <row r="34" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>24</v>
       </c>
@@ -10027,21 +10080,21 @@
         <f aca="false">I34/2+G34</f>
         <v>14</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="L34" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C34,E34,J34),0)</f>
         <v>11</v>
       </c>
-      <c r="M34" s="1" t="str">
+      <c r="M34" s="9" t="str">
         <f aca="false">IF(L34&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
       <c r="N34" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="P34" s="21" t="n">
+      <c r="P34" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="Q34" s="22" t="n">
+      <c r="Q34" s="4" t="n">
         <v>45849</v>
       </c>
       <c r="R34" s="1" t="n">
@@ -10054,7 +10107,7 @@
         <f aca="false">S34+T34/2</f>
         <v>9</v>
       </c>
-      <c r="V34" s="23" t="n">
+      <c r="V34" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U34,R34,P34,N34,L34),0)</f>
         <v>9</v>
       </c>
@@ -10062,14 +10115,14 @@
         <f aca="false">ROUND(AVERAGE(C34,E34,J34,N34,P34,R34,S34),0)</f>
         <v>9</v>
       </c>
-      <c r="Y34" s="18" t="n">
+      <c r="Y34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="Z34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AC34" s="1" t="n">
         <v>7</v>
@@ -10081,126 +10134,130 @@
         <f aca="false">AE34+AF34/2</f>
         <v>8</v>
       </c>
-      <c r="AI34" s="11" t="n">
+      <c r="AI34" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y34,Z34,AC34,AG34),0)</f>
         <v>9</v>
       </c>
       <c r="AL34" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AQ34" s="11" t="n">
+      <c r="AQ34" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V34,AI34),0)</f>
         <v>9</v>
       </c>
-      <c r="AR34" s="11"/>
-    </row>
-    <row r="35" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="n">
+      <c r="AR34" s="9"/>
+      <c r="AT34" s="9"/>
+    </row>
+    <row r="35" s="1" customFormat="true" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" s="19" t="n">
+      <c r="C35" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="F35" s="25" t="n">
+      <c r="F35" s="4" t="n">
         <v>45994</v>
       </c>
-      <c r="G35" s="24" t="n">
+      <c r="G35" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H35" s="25" t="n">
+      <c r="H35" s="4" t="n">
         <v>46001</v>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="2" t="n">
+      <c r="I35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="n">
         <f aca="false">I35/2+G35</f>
         <v>7</v>
       </c>
-      <c r="L35" s="23" t="n">
+      <c r="L35" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(C35,E35,J35),0)</f>
         <v>8</v>
       </c>
-      <c r="M35" s="23" t="str">
+      <c r="M35" s="9" t="str">
         <f aca="false">IF(L35&gt;6,"TEA","TEP")</f>
         <v>TEA</v>
       </c>
-      <c r="N35" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P35" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="R35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" s="2" t="n">
+      <c r="N35" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="U35" s="2" t="n">
+      <c r="U35" s="1" t="n">
         <f aca="false">S35+T35/2</f>
         <v>6</v>
       </c>
-      <c r="V35" s="23" t="n">
+      <c r="V35" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(U35,R35,P35,N35,L35),0)</f>
         <v>6</v>
       </c>
-      <c r="W35" s="2" t="n">
+      <c r="W35" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C35,E35,J35,N35,P35,R35,S35),0)</f>
         <v>7</v>
       </c>
-      <c r="X35" s="2" t="s">
+      <c r="X35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Y35" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z35" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA35" s="25" t="n">
+      <c r="Y35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA35" s="4" t="n">
         <v>46001</v>
       </c>
-      <c r="AB35" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AC35" s="24" t="n">
+      <c r="AB35" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC35" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AD35" s="25" t="n">
+      <c r="AD35" s="4" t="n">
         <v>46001</v>
       </c>
-      <c r="AE35" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG35" s="2" t="n">
+      <c r="AE35" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG35" s="1" t="n">
         <f aca="false">AE35+AF35/2</f>
         <v>8</v>
       </c>
-      <c r="AI35" s="23" t="n">
+      <c r="AI35" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(Y35,Z35,AC35,AG35),0)</f>
         <v>8</v>
       </c>
-      <c r="AQ35" s="23" t="n">
+      <c r="AQ35" s="9" t="n">
         <f aca="false">ROUND(AVERAGE(V35,AI35),0)</f>
         <v>7</v>
       </c>
-      <c r="AR35" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS35" s="2" t="n">
+      <c r="AR35" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS35" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C35,E35,G35,P35,Y35,Z35,AC35),0)</f>
         <v>8</v>
       </c>
-      <c r="AT35" s="2" t="n">
+      <c r="AT35" s="9" t="n">
         <f aca="false">ROUND(AS35*6/10,0)</f>
         <v>5</v>
+      </c>
+      <c r="AU35" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -10281,15 +10338,19 @@
     <cfRule type="cellIs" priority="19" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>7</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P11:P35">
     <cfRule type="cellIs" priority="20" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>7</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P11:P35">
     <cfRule type="cellIs" priority="21" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>7</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AT11:AT35">
+    <cfRule type="cellIs" priority="22" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>3</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -10321,7 +10382,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>5</v>
@@ -10342,10 +10403,10 @@
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J1" s="4" t="n">
         <v>45777</v>
@@ -10363,25 +10424,25 @@
         <v>45840</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="R1" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="R1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10405,7 +10466,7 @@
         <f aca="false">G2+H2</f>
         <v>2</v>
       </c>
-      <c r="O2" s="30" t="n">
+      <c r="O2" s="24" t="n">
         <f aca="false">SUM(N2,M2,L2,K2,J2,I2,H2,G2)</f>
         <v>4</v>
       </c>
@@ -10425,7 +10486,7 @@
         <f aca="false">G3+H3</f>
         <v>0</v>
       </c>
-      <c r="O3" s="30" t="n">
+      <c r="O3" s="24" t="n">
         <f aca="false">SUM(N3,M3,L3,K3,J3,I3,H3,G3)</f>
         <v>0</v>
       </c>
@@ -10457,7 +10518,7 @@
       <c r="J4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="O4" s="30" t="n">
+      <c r="O4" s="24" t="n">
         <f aca="false">SUM(N4,M4,L4,K4,J4,I4,H4,G4)</f>
         <v>33</v>
       </c>
@@ -10486,14 +10547,14 @@
       <c r="J5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="O5" s="30" t="n">
+      <c r="O5" s="24" t="n">
         <f aca="false">SUM(N5,M5,L5,K5,J5,I5,H5,G5)</f>
         <v>15</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="R5" s="16" t="n">
+      <c r="R5" s="12" t="n">
         <f aca="false">SUM(P5:Q5)</f>
         <v>20</v>
       </c>
@@ -10519,11 +10580,11 @@
         <f aca="false">G6+H6</f>
         <v>4</v>
       </c>
-      <c r="O6" s="30" t="n">
+      <c r="O6" s="24" t="n">
         <f aca="false">SUM(N6,M6,L6,K6,J6,I6,H6,G6)</f>
         <v>8</v>
       </c>
-      <c r="R6" s="16" t="n">
+      <c r="R6" s="12" t="n">
         <f aca="false">SUM(P6:Q6)</f>
         <v>0</v>
       </c>
@@ -10543,11 +10604,11 @@
         <f aca="false">G7+H7</f>
         <v>0</v>
       </c>
-      <c r="O7" s="30" t="n">
+      <c r="O7" s="24" t="n">
         <f aca="false">SUM(N7,M7,L7,K7,J7,I7,H7,G7)</f>
         <v>0</v>
       </c>
-      <c r="R7" s="16" t="n">
+      <c r="R7" s="12" t="n">
         <f aca="false">SUM(P7:Q7)</f>
         <v>0</v>
       </c>
@@ -10582,11 +10643,11 @@
       <c r="K8" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="O8" s="30" t="n">
+      <c r="O8" s="24" t="n">
         <f aca="false">SUM(N8,M8,L8,K8,J8,I8,H8,G8)</f>
         <v>20</v>
       </c>
-      <c r="R8" s="16" t="n">
+      <c r="R8" s="12" t="n">
         <f aca="false">SUM(P8:Q8)</f>
         <v>0</v>
       </c>
@@ -10609,11 +10670,11 @@
         <f aca="false">G9+H9</f>
         <v>6</v>
       </c>
-      <c r="O9" s="30" t="n">
+      <c r="O9" s="24" t="n">
         <f aca="false">SUM(N9,M9,L9,K9,J9,I9,H9,G9)</f>
         <v>12</v>
       </c>
-      <c r="R9" s="16" t="n">
+      <c r="R9" s="12" t="n">
         <f aca="false">SUM(P9:Q9)</f>
         <v>0</v>
       </c>
@@ -10654,14 +10715,14 @@
       <c r="N10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O10" s="30" t="n">
+      <c r="O10" s="24" t="n">
         <f aca="false">SUM(N10,M10,L10,K10,J10,I10,H10,G10)</f>
         <v>35</v>
       </c>
       <c r="P10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="12" t="n">
         <f aca="false">SUM(P10:Q10)</f>
         <v>10</v>
       </c>
@@ -10696,14 +10757,14 @@
       <c r="N11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O11" s="30" t="n">
+      <c r="O11" s="24" t="n">
         <f aca="false">SUM(N11,M11,L11,K11,J11,I11,H11,G11)</f>
         <v>14</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="R11" s="16" t="n">
+      <c r="R11" s="12" t="n">
         <f aca="false">SUM(P11:Q11)</f>
         <v>86</v>
       </c>
@@ -10753,11 +10814,11 @@
       <c r="N12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="30" t="n">
+      <c r="O12" s="24" t="n">
         <f aca="false">SUM(N12,M12,L12,K12,J12,I12,H12,G12)</f>
         <v>24</v>
       </c>
-      <c r="R12" s="16" t="n">
+      <c r="R12" s="12" t="n">
         <f aca="false">SUM(P12:Q12)</f>
         <v>0</v>
       </c>
@@ -10777,7 +10838,7 @@
         <f aca="false">G13+H13</f>
         <v>0</v>
       </c>
-      <c r="O13" s="30" t="n">
+      <c r="O13" s="24" t="n">
         <f aca="false">SUM(N13,M13,L13,K13,J13,I13,H13,G13)</f>
         <v>0</v>
       </c>
@@ -10787,7 +10848,7 @@
       <c r="Q13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="16" t="n">
+      <c r="R13" s="12" t="n">
         <f aca="false">SUM(P13:Q13)</f>
         <v>70</v>
       </c>
@@ -10828,7 +10889,7 @@
       <c r="J14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="O14" s="30" t="n">
+      <c r="O14" s="24" t="n">
         <f aca="false">SUM(N14,M14,L14,K14,J14,I14,H14,G14)</f>
         <v>87</v>
       </c>
@@ -10838,7 +10899,7 @@
       <c r="Q14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R14" s="16" t="n">
+      <c r="R14" s="12" t="n">
         <f aca="false">SUM(P14:Q14)</f>
         <v>46</v>
       </c>
@@ -10882,7 +10943,7 @@
       <c r="L15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="O15" s="30" t="n">
+      <c r="O15" s="24" t="n">
         <f aca="false">SUM(N15,M15,L15,K15,J15,I15,H15,G15)</f>
         <v>62</v>
       </c>
@@ -10892,7 +10953,7 @@
       <c r="Q15" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R15" s="16" t="n">
+      <c r="R15" s="12" t="n">
         <f aca="false">SUM(P15:Q15)</f>
         <v>76</v>
       </c>
@@ -10918,11 +10979,11 @@
       <c r="L16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O16" s="30" t="n">
+      <c r="O16" s="24" t="n">
         <f aca="false">SUM(N16,M16,L16,K16,J16,I16,H16,G16)</f>
         <v>3</v>
       </c>
-      <c r="R16" s="16" t="n">
+      <c r="R16" s="12" t="n">
         <f aca="false">SUM(P16:Q16)</f>
         <v>0</v>
       </c>
@@ -10945,11 +11006,11 @@
         <f aca="false">G17+H17</f>
         <v>1</v>
       </c>
-      <c r="O17" s="30" t="n">
+      <c r="O17" s="24" t="n">
         <f aca="false">SUM(N17,M17,L17,K17,J17,I17,H17,G17)</f>
         <v>2</v>
       </c>
-      <c r="R17" s="16" t="n">
+      <c r="R17" s="12" t="n">
         <f aca="false">SUM(P17:Q17)</f>
         <v>0</v>
       </c>
@@ -10975,11 +11036,11 @@
       <c r="K18" s="1" t="n">
         <v>-1</v>
       </c>
-      <c r="O18" s="30" t="n">
+      <c r="O18" s="24" t="n">
         <f aca="false">SUM(N18,M18,L18,K18,J18,I18,H18,G18)</f>
         <v>1</v>
       </c>
-      <c r="R18" s="16" t="n">
+      <c r="R18" s="12" t="n">
         <f aca="false">SUM(P18:Q18)</f>
         <v>0</v>
       </c>
@@ -11014,11 +11075,11 @@
       <c r="L19" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="O19" s="30" t="n">
+      <c r="O19" s="24" t="n">
         <f aca="false">SUM(N19,M19,L19,K19,J19,I19,H19,G19)</f>
         <v>25</v>
       </c>
-      <c r="R19" s="16" t="n">
+      <c r="R19" s="12" t="n">
         <f aca="false">SUM(P19:Q19)</f>
         <v>0</v>
       </c>
@@ -11041,11 +11102,11 @@
       <c r="J20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="O20" s="30" t="n">
+      <c r="O20" s="24" t="n">
         <f aca="false">SUM(N20,M20,L20,K20,J20,I20,H20,G20)</f>
         <v>2</v>
       </c>
-      <c r="R20" s="16" t="n">
+      <c r="R20" s="12" t="n">
         <f aca="false">SUM(P20:Q20)</f>
         <v>0</v>
       </c>
@@ -11074,11 +11135,11 @@
       <c r="J21" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="O21" s="30" t="n">
+      <c r="O21" s="24" t="n">
         <f aca="false">SUM(N21,M21,L21,K21,J21,I21,H21,G21)</f>
         <v>8</v>
       </c>
-      <c r="R21" s="16" t="n">
+      <c r="R21" s="12" t="n">
         <f aca="false">SUM(P21:Q21)</f>
         <v>0</v>
       </c>
@@ -11104,11 +11165,11 @@
         <f aca="false">G22+H22</f>
         <v>5</v>
       </c>
-      <c r="O22" s="30" t="n">
+      <c r="O22" s="24" t="n">
         <f aca="false">SUM(N22,M22,L22,K22,J22,I22,H22,G22)</f>
         <v>10</v>
       </c>
-      <c r="R22" s="16" t="n">
+      <c r="R22" s="12" t="n">
         <f aca="false">SUM(P22:Q22)</f>
         <v>0</v>
       </c>
@@ -11140,11 +11201,11 @@
       <c r="N23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O23" s="30" t="n">
+      <c r="O23" s="24" t="n">
         <f aca="false">SUM(N23,M23,L23,K23,J23,I23,H23,G23)</f>
         <v>20</v>
       </c>
-      <c r="R23" s="16" t="n">
+      <c r="R23" s="12" t="n">
         <f aca="false">SUM(P23:Q23)</f>
         <v>0</v>
       </c>
@@ -11185,7 +11246,7 @@
       <c r="L24" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="O24" s="30" t="n">
+      <c r="O24" s="24" t="n">
         <f aca="false">SUM(N24,M24,L24,K24,J24,I24,H24,G24)</f>
         <v>97</v>
       </c>
@@ -11195,7 +11256,7 @@
       <c r="Q24" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="12" t="n">
         <f aca="false">SUM(P24:Q24)</f>
         <v>76</v>
       </c>
@@ -11242,7 +11303,7 @@
       <c r="N25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O25" s="30" t="n">
+      <c r="O25" s="24" t="n">
         <f aca="false">SUM(N25,M25,L25,K25,J25,I25,H25,G25)</f>
         <v>103</v>
       </c>
@@ -11252,7 +11313,7 @@
       <c r="Q25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R25" s="16" t="n">
+      <c r="R25" s="12" t="n">
         <f aca="false">SUM(P25:Q25)</f>
         <v>120</v>
       </c>
@@ -11284,14 +11345,14 @@
       <c r="L26" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="O26" s="30" t="n">
+      <c r="O26" s="24" t="n">
         <f aca="false">SUM(N26,M26,L26,K26,J26,I26,H26,G26)</f>
         <v>14</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="R26" s="16" t="n">
+      <c r="R26" s="12" t="n">
         <f aca="false">SUM(P26:Q26)</f>
         <v>10</v>
       </c>
@@ -11310,7 +11371,7 @@
         <f aca="false">G27+H27</f>
         <v>0</v>
       </c>
-      <c r="O27" s="30" t="n">
+      <c r="O27" s="24" t="n">
         <f aca="false">SUM(N27,M27,L27,K27,J27,I27,H27,G27)</f>
         <v>0</v>
       </c>
@@ -11349,25 +11410,25 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11803,19 +11864,19 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11829,7 +11890,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>9</v>
@@ -11860,7 +11921,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>8</v>
@@ -11880,7 +11941,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>10</v>
@@ -11900,7 +11961,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>8</v>
@@ -11931,7 +11992,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>10</v>
@@ -11951,7 +12012,7 @@
         <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>8</v>
@@ -11971,7 +12032,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>9</v>
@@ -11991,7 +12052,7 @@
         <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>5</v>
@@ -12011,7 +12072,7 @@
         <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>9</v>
@@ -12042,7 +12103,7 @@
         <v>60</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>9</v>
@@ -12062,7 +12123,7 @@
         <v>63</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>10</v>
@@ -12082,7 +12143,7 @@
         <v>66</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>8</v>
@@ -12102,7 +12163,7 @@
         <v>69</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>10</v>
@@ -12122,7 +12183,7 @@
         <v>72</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>10</v>
@@ -12142,7 +12203,7 @@
         <v>75</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>8</v>
@@ -12162,7 +12223,7 @@
         <v>78</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>10</v>
@@ -12187,7 +12248,7 @@
         <v>78</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>6</v>
@@ -12215,7 +12276,7 @@
         <v>86</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>10</v>
@@ -12240,7 +12301,7 @@
         <v>86</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>9</v>
@@ -12254,7 +12315,7 @@
         <v>86</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>7</v>
@@ -12268,7 +12329,7 @@
         <v>86</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>1</v>
@@ -12285,7 +12346,7 @@
         <v>89</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>10</v>
@@ -12305,7 +12366,7 @@
         <v>92</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E28" s="1" t="n">
         <v>10</v>
@@ -12325,7 +12386,7 @@
         <v>95</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E29" s="1" t="n">
         <v>10</v>
@@ -12350,12 +12411,12 @@
         <v>95</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E30" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="F30" s="10"/>
+      <c r="F30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
@@ -12365,7 +12426,7 @@
         <v>95</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E31" s="1" t="n">
         <v>2</v>
@@ -12382,7 +12443,7 @@
         <v>98</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>8</v>
@@ -12402,7 +12463,7 @@
         <v>101</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E33" s="1" t="n">
         <v>10</v>
@@ -12440,19 +12501,19 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12463,7 +12524,7 @@
         <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>9</v>
@@ -12491,7 +12552,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>4</v>
@@ -12513,7 +12574,7 @@
         <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>2</v>
@@ -12527,7 +12588,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>7</v>
@@ -12544,7 +12605,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>8</v>
@@ -12561,7 +12622,7 @@
         <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>7</v>
@@ -12578,7 +12639,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -12606,7 +12667,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>10</v>
@@ -12628,7 +12689,7 @@
         <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
@@ -12639,7 +12700,7 @@
         <v>49</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>6</v>
@@ -12650,7 +12711,7 @@
         <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>4</v>
@@ -12661,7 +12722,7 @@
         <v>49</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>3</v>
@@ -12675,7 +12736,7 @@
         <v>52</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>6</v>
@@ -12692,7 +12753,7 @@
         <v>55</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>9</v>
@@ -12709,7 +12770,7 @@
         <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>4</v>
@@ -12731,7 +12792,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>2</v>
@@ -12745,7 +12806,7 @@
         <v>61</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>10</v>
@@ -12762,7 +12823,7 @@
         <v>64</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -12784,7 +12845,7 @@
         <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>7</v>
@@ -12795,7 +12856,7 @@
         <v>64</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>5</v>
@@ -12806,7 +12867,7 @@
         <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>4</v>
@@ -12820,7 +12881,7 @@
         <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>8</v>
@@ -12848,7 +12909,7 @@
         <v>73</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>8</v>
@@ -12865,7 +12926,7 @@
         <v>76</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>9</v>
@@ -12882,7 +12943,7 @@
         <v>79</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>10</v>
@@ -12910,7 +12971,7 @@
         <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>8</v>
@@ -12927,7 +12988,7 @@
         <v>90</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>10</v>
@@ -12944,7 +13005,7 @@
         <v>93</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>10</v>
@@ -12961,7 +13022,7 @@
         <v>96</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>10</v>
@@ -12983,7 +13044,7 @@
         <v>96</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>10</v>
@@ -12994,7 +13055,7 @@
         <v>96</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>9</v>
@@ -13005,7 +13066,7 @@
         <v>96</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>9</v>
@@ -13016,7 +13077,7 @@
         <v>96</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>9</v>
@@ -13027,7 +13088,7 @@
         <v>96</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>9</v>
@@ -13038,7 +13099,7 @@
         <v>96</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>8</v>
@@ -13052,7 +13113,7 @@
         <v>99</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>10</v>
@@ -13109,19 +13170,19 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13132,7 +13193,7 @@
         <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>7</v>
@@ -13171,7 +13232,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>7</v>
@@ -13188,7 +13249,7 @@
         <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>9</v>
@@ -13205,7 +13266,7 @@
         <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>9</v>
@@ -13227,7 +13288,7 @@
         <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>9</v>
@@ -13238,7 +13299,7 @@
         <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>7</v>
@@ -13249,7 +13310,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>7</v>
@@ -13260,7 +13321,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>6</v>
@@ -13271,7 +13332,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>6</v>
@@ -13282,7 +13343,7 @@
         <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>6</v>
@@ -13293,7 +13354,7 @@
         <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>4</v>
@@ -13304,7 +13365,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>3</v>
@@ -13318,7 +13379,7 @@
         <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>5</v>
@@ -13346,7 +13407,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9</v>
@@ -13363,7 +13424,7 @@
         <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>7</v>
@@ -13385,7 +13446,7 @@
         <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>6</v>
@@ -13396,7 +13457,7 @@
         <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>6</v>
@@ -13407,7 +13468,7 @@
         <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>5</v>
@@ -13418,7 +13479,7 @@
         <v>52</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>3</v>
@@ -13429,7 +13490,7 @@
         <v>52</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>2</v>
@@ -13443,7 +13504,7 @@
         <v>55</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>9</v>
@@ -13465,7 +13526,7 @@
         <v>55</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>6</v>
@@ -13479,7 +13540,7 @@
         <v>58</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>8</v>
@@ -13496,7 +13557,7 @@
         <v>61</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>9</v>
@@ -13518,7 +13579,7 @@
         <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>7</v>
@@ -13529,7 +13590,7 @@
         <v>61</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>6</v>
@@ -13540,7 +13601,7 @@
         <v>61</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>6</v>
@@ -13554,7 +13615,7 @@
         <v>64</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>5</v>
@@ -13576,7 +13637,7 @@
         <v>64</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>5</v>
@@ -13587,7 +13648,7 @@
         <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>5</v>
@@ -13598,7 +13659,7 @@
         <v>64</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>4</v>
@@ -13623,7 +13684,7 @@
         <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>8</v>
@@ -13645,7 +13706,7 @@
         <v>70</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>8</v>
@@ -13656,7 +13717,7 @@
         <v>70</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>7</v>
@@ -13667,7 +13728,7 @@
         <v>70</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>3</v>
@@ -13681,7 +13742,7 @@
         <v>73</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>9</v>
@@ -13698,7 +13759,7 @@
         <v>73</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>5</v>
@@ -13715,7 +13776,7 @@
         <v>79</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>10</v>
@@ -13743,7 +13804,7 @@
         <v>87</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>7</v>
@@ -13760,7 +13821,7 @@
         <v>90</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>9</v>
@@ -13782,7 +13843,7 @@
         <v>90</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>9</v>
@@ -13796,7 +13857,7 @@
         <v>93</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>10</v>
@@ -13813,7 +13874,7 @@
         <v>96</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>10</v>
@@ -13830,7 +13891,7 @@
         <v>99</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>7</v>
@@ -13847,7 +13908,7 @@
         <v>102</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>5</v>
@@ -13888,22 +13949,22 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13911,10 +13972,10 @@
         <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>2.5</v>
@@ -13928,10 +13989,10 @@
         <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>8.75</v>
@@ -13953,10 +14014,10 @@
         <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>7.5</v>
@@ -13967,10 +14028,10 @@
         <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>5</v>
@@ -13981,10 +14042,10 @@
         <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>3.75</v>
@@ -13995,10 +14056,10 @@
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>2.5</v>
@@ -14009,10 +14070,10 @@
         <v>58</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>7.5</v>
@@ -14026,10 +14087,10 @@
         <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -14051,10 +14112,10 @@
         <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>8.75</v>
@@ -14065,10 +14126,10 @@
         <v>70</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>3.75</v>
@@ -14079,10 +14140,10 @@
         <v>70</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1.25</v>
@@ -14118,22 +14179,22 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14141,10 +14202,10 @@
         <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>2.5</v>
@@ -14158,10 +14219,10 @@
         <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>8.75</v>
@@ -14183,10 +14244,10 @@
         <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>7.5</v>
@@ -14197,10 +14258,10 @@
         <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>5</v>
@@ -14211,10 +14272,10 @@
         <v>67</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>8.75</v>
